--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,6 +1529,113 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113440367</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79102</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stensmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>779150</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7201841</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
+        <v>79118</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79118</v>
+        <v>79130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79130</v>
+        <v>79152</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>79162</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79162</v>
+        <v>79169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>113440367</v>
       </c>
       <c r="B10" t="n">
-        <v>79171</v>
+        <v>79199</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112934805</v>
+        <v>112934810</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skellefteå kommun, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>779241</v>
+        <v>779189</v>
       </c>
       <c r="R2" t="n">
-        <v>7201576</v>
+        <v>7201826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112934814</v>
+        <v>112934808</v>
       </c>
       <c r="B3" t="n">
-        <v>96140</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779288</v>
+        <v>779199</v>
       </c>
       <c r="R3" t="n">
-        <v>7201874</v>
+        <v>7201549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 dm2</t>
+          <t>Lågt på levande tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112934813</v>
+        <v>113440416</v>
       </c>
       <c r="B4" t="n">
-        <v>97097</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skellefteå kommun, Vb</t>
+          <t>Stensmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779276</v>
+        <v>779120</v>
       </c>
       <c r="R4" t="n">
-        <v>7201883</v>
+        <v>7201836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>Sweco naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,31 +969,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112934809</v>
+        <v>112934807</v>
       </c>
       <c r="B5" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779142</v>
+        <v>779205</v>
       </c>
       <c r="R5" t="n">
-        <v>7201668</v>
+        <v>7201520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,55 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112934812</v>
+        <v>112934809</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skellefteå kommun, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779212</v>
+        <v>779142</v>
       </c>
       <c r="R6" t="n">
-        <v>7201833</v>
+        <v>7201669</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack lågt på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,50 +1175,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112934808</v>
+        <v>113440366</v>
       </c>
       <c r="B7" t="n">
-        <v>89969</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skellefteå kommun, Vb</t>
+          <t>Stensmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779199</v>
+        <v>779122</v>
       </c>
       <c r="R7" t="n">
-        <v>7201549</v>
+        <v>7201834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,17 +1240,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lågt på levande tall</t>
+          <t>Sweco naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,62 +1265,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112934810</v>
+        <v>113440367</v>
       </c>
       <c r="B8" t="n">
-        <v>89945</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skellefteå kommun, Vb</t>
+          <t>Stensmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779189</v>
+        <v>779150</v>
       </c>
       <c r="R8" t="n">
-        <v>7201826</v>
+        <v>7201842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1342,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>Sweco naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,31 +1367,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112934815</v>
+        <v>112934805</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1465,7 +1410,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1474,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779335</v>
+        <v>779241</v>
       </c>
       <c r="R9" t="n">
-        <v>7201893</v>
+        <v>7201576</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,50 +1486,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112934807</v>
+        <v>112934806</v>
       </c>
       <c r="B10" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skellefteå kommun, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>779204</v>
+        <v>779229</v>
       </c>
       <c r="R10" t="n">
-        <v>7201520</v>
+        <v>7201521</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113440367</v>
+        <v>112934812</v>
       </c>
       <c r="B11" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1604,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stensmyran, Vb</t>
+          <t>Skellefteå kommun, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779150</v>
+        <v>779212</v>
       </c>
       <c r="R11" t="n">
-        <v>7201842</v>
+        <v>7201833</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1663,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sweco naturvärdesinventering</t>
+          <t>Hack lågt på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,15 +1688,423 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Linda Sandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Linda Sandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112934815</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skellefteå kommun, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>779335</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7201893</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112934855</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skellefteå kommun, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>778844</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7200933</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112934814</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skellefteå kommun, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>779287</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7201874</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112934813</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skellefteå kommun, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>779275</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7201883</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 st</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54391-2023 artfynd.xlsx
+++ b/artfynd/A 54391-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934810</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440416</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934809</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440366</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440367</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934815</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934855</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934814</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,8 +2175,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>